--- a/data/trans_dic/IP31KM10_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM10_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,63; 55,24</t>
+          <t>32,05; 53,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,48; 51,77</t>
+          <t>32,92; 52,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,35; 50,0</t>
+          <t>35,58; 50,23</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,41; 82,38</t>
+          <t>36,79; 56,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,48; 55,41</t>
+          <t>33,22; 51,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,14; 66,81</t>
+          <t>37,84; 51,35</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,35; 42,23</t>
+          <t>38,79; 59,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,19; 58,31</t>
+          <t>23,09; 41,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,74; 47,59</t>
+          <t>33,9; 48,78</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,5; 39,07</t>
+          <t>39,84; 71,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,16; 74,11</t>
+          <t>21,01; 41,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,12; 56,1</t>
+          <t>31,54; 52,98</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,35; 76,77</t>
+          <t>59,75; 80,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,4; 82,03</t>
+          <t>52,97; 76,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60,89; 76,05</t>
+          <t>60,36; 75,2</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,46; 44,61</t>
+          <t>24,41; 45,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,55; 45,07</t>
+          <t>23,74; 45,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,48; 40,95</t>
+          <t>27,26; 42,48</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,35; 54,22</t>
+          <t>37,61; 53,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,52; 53,0</t>
+          <t>38,32; 54,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,83; 51,48</t>
+          <t>40,33; 51,72</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>79,73; 90,3</t>
+          <t>87,23; 95,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,94; 94,97</t>
+          <t>78,0; 90,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,44; 91,91</t>
+          <t>85,05; 91,68</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>48,56; 58,75</t>
+          <t>54,18; 61,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52,95; 60,33</t>
+          <t>47,92; 54,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,98; 58,06</t>
+          <t>52,35; 57,17</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30637</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>23545</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60998</t>
+          <t>49591</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21867; 39444</t>
+          <t>19313; 32343</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22739; 38628</t>
+          <t>18080; 28945</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48694; 73003</t>
+          <t>40982; 57860</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>53248</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>58870</t>
+          <t>42143</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128049</t>
+          <t>95390</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49514; 103509</t>
+          <t>42293; 64399</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46122; 70051</t>
+          <t>32995; 51392</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106213; 168414</t>
+          <t>81079; 110039</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>28317</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>45883</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12972; 23461</t>
+          <t>22227; 33860</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24683; 37688</t>
+          <t>12495; 22503</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39352; 57193</t>
+          <t>37763; 54347</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>37096</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60672</t>
+          <t>58029</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13587; 27223</t>
+          <t>27817; 49883</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30265; 55857</t>
+          <t>14802; 29065</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48044; 81369</t>
+          <t>44243; 74323</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>28015</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29350</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51791</t>
+          <t>51166</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18246; 26256</t>
+          <t>23648; 31863</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24594; 33402</t>
+          <t>18734; 27008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45622; 56977</t>
+          <t>45236; 56362</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>31144</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9946; 19759</t>
+          <t>11523; 21428</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12667; 24241</t>
+          <t>10512; 20151</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25974; 40162</t>
+          <t>24942; 38867</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>57463</t>
+          <t>63515</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>69768</t>
+          <t>56764</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127231</t>
+          <t>120279</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>47433; 67073</t>
+          <t>52863; 74849</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>56629; 82171</t>
+          <t>46687; 66023</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>111009; 143506</t>
+          <t>105820; 135713</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>158</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>110279</t>
+          <t>144496</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>141462</t>
+          <t>117769</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>251740</t>
+          <t>262265</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>102587; 116190</t>
+          <t>137063; 149778</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134028; 146403</t>
+          <t>107569; 124626</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>241647; 259942</t>
+          <t>250915; 270484</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>459</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>342390</t>
+          <t>396963</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>316782</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>762210</t>
+          <t>713745</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>317176; 383688</t>
+          <t>372106; 422138</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>394361; 449275</t>
+          <t>296244; 339309</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>726618; 811629</t>
+          <t>683147; 746073</t>
         </is>
       </c>
     </row>
